--- a/outputs/Заказ покупателю.xlsx
+++ b/outputs/Заказ покупателю.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13322529</v>
+        <v>12449745</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30000</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="5">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-33742</v>
+        <v>-906526</v>
       </c>
     </row>
   </sheetData>
@@ -789,32 +789,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>3239</v>
+        <v>7279</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>3000</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>436.392</v>
+        <v>397.133</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1309176</v>
+        <v>1191399</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>239</v>
+        <v>4279</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>239</v>
+        <v>4279</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>400</v>
+        <v>1800</v>
       </c>
       <c r="J7" t="n">
         <v>2028</v>
@@ -823,32 +823,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
+          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>7279</v>
+        <v>6179</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>3000</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>397.133</v>
+        <v>382.536</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1191399</v>
+        <v>1147608</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4279</v>
+        <v>3179</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4279</v>
+        <v>3179</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1800</v>
+        <v>4000</v>
       </c>
       <c r="J8" t="n">
         <v>2028</v>
@@ -857,32 +857,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
+          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>6179</v>
+        <v>7463</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>3000</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>382.536</v>
+        <v>222.497</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1147608</v>
+        <v>667491</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3179</v>
+        <v>4463</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3179</v>
+        <v>4463</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4000</v>
+        <v>600</v>
       </c>
       <c r="J9" t="n">
         <v>2028</v>
@@ -891,32 +891,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>7463</v>
+        <v>7340</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>3000</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>222.497</v>
+        <v>177.43</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>667491</v>
+        <v>532290</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4463</v>
+        <v>4340</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4463</v>
+        <v>4340</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="J10" t="n">
         <v>2028</v>
@@ -925,32 +925,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>7340</v>
+        <v>3239</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>177.43</v>
+        <v>436.392</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>532290</v>
+        <v>436392</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4340</v>
+        <v>2239</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4340</v>
+        <v>2239</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="J11" t="n">
         <v>2028</v>
@@ -966,20 +966,20 @@
         <v>59244</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>30000</v>
+        <v>28000</v>
       </c>
       <c r="D12" s="6" t="inlineStr"/>
       <c r="E12" s="6" t="n">
-        <v>13322529</v>
+        <v>12449745</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>29244</v>
+        <v>31244</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>65028</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>94272</v>
+        <v>96272</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>12800</v>

--- a/outputs/Заказ покупателю.xlsx
+++ b/outputs/Заказ покупателю.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12449745</v>
+        <v>13331417</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="5">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-906526</v>
+        <v>-24854</v>
       </c>
     </row>
   </sheetData>
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -857,32 +857,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
+          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>7463</v>
+        <v>2435</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>222.497</v>
+        <v>440.836</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>667491</v>
+        <v>881672</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4463</v>
+        <v>435</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4463</v>
+        <v>435</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="J9" t="n">
         <v>2028</v>
@@ -891,32 +891,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
+          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>7340</v>
+        <v>7463</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>3000</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>177.43</v>
+        <v>222.497</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>532290</v>
+        <v>667491</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4340</v>
+        <v>4463</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4340</v>
+        <v>4463</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2000</v>
+        <v>600</v>
       </c>
       <c r="J10" t="n">
         <v>2028</v>
@@ -925,66 +925,100 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>3239</v>
+        <v>7340</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>436.392</v>
+        <v>177.43</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>436392</v>
+        <v>532290</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2239</v>
+        <v>4340</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2239</v>
+        <v>4340</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="J11" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>3239</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>436.392</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>436392</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>2239</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>2239</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
-        <v>59244</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>28000</v>
-      </c>
-      <c r="D12" s="6" t="inlineStr"/>
-      <c r="E12" s="6" t="n">
-        <v>12449745</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>31244</v>
-      </c>
-      <c r="G12" s="6" t="n">
+      <c r="B13" s="6" t="n">
+        <v>61679</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr"/>
+      <c r="E13" s="6" t="n">
+        <v>13331417</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>31679</v>
+      </c>
+      <c r="G13" s="6" t="n">
         <v>65028</v>
       </c>
-      <c r="H12" s="6" t="n">
-        <v>96272</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>12800</v>
-      </c>
-      <c r="J12" s="5" t="inlineStr"/>
+      <c r="H13" s="6" t="n">
+        <v>96707</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>13200</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/Заказ покупателю.xlsx
+++ b/outputs/Заказ покупателю.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13331417</v>
+        <v>12890581</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30000</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="5">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-24854</v>
+        <v>-465690</v>
       </c>
     </row>
   </sheetData>
@@ -857,32 +857,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
+          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2435</v>
+        <v>7463</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>440.836</v>
+        <v>222.497</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>881672</v>
+        <v>667491</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>435</v>
+        <v>4463</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>435</v>
+        <v>4463</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="J9" t="n">
         <v>2028</v>
@@ -891,32 +891,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>7463</v>
+        <v>7340</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>3000</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>222.497</v>
+        <v>177.43</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>667491</v>
+        <v>532290</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4463</v>
+        <v>4340</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4463</v>
+        <v>4340</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="J10" t="n">
         <v>2028</v>
@@ -925,32 +925,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
+          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>7340</v>
+        <v>2435</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>177.43</v>
+        <v>440.836</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>532290</v>
+        <v>440836</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4340</v>
+        <v>1435</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4340</v>
+        <v>1435</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="J11" t="n">
         <v>2028</v>
@@ -1000,20 +1000,20 @@
         <v>61679</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>30000</v>
+        <v>29000</v>
       </c>
       <c r="D13" s="6" t="inlineStr"/>
       <c r="E13" s="6" t="n">
-        <v>13331417</v>
+        <v>12890581</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>31679</v>
+        <v>32679</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>65028</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>96707</v>
+        <v>97707</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>13200</v>

--- a/outputs/Заказ покупателю.xlsx
+++ b/outputs/Заказ покупателю.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12890581</v>
+        <v>12377509</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29000</v>
+        <v>28040</v>
       </c>
     </row>
     <row r="5">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-465690</v>
+        <v>-978762</v>
       </c>
     </row>
   </sheetData>
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -755,32 +755,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>3493</v>
+        <v>7279</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>3000</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>436.392</v>
+        <v>397.133</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1309176</v>
+        <v>1191399</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>493</v>
+        <v>4279</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>493</v>
+        <v>4279</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>800</v>
+        <v>1800</v>
       </c>
       <c r="J6" t="n">
         <v>2028</v>
@@ -789,32 +789,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
+          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>7279</v>
+        <v>6179</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>3000</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>397.133</v>
+        <v>382.536</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1191399</v>
+        <v>1147608</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4279</v>
+        <v>3179</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4279</v>
+        <v>3179</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1800</v>
+        <v>4000</v>
       </c>
       <c r="J7" t="n">
         <v>2028</v>
@@ -823,32 +823,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
+          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>6179</v>
+        <v>7463</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>3000</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>382.536</v>
+        <v>222.497</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1147608</v>
+        <v>667491</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3179</v>
+        <v>4463</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3179</v>
+        <v>4463</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4000</v>
+        <v>600</v>
       </c>
       <c r="J8" t="n">
         <v>2028</v>
@@ -857,32 +857,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>7463</v>
+        <v>7340</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>3000</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>222.497</v>
+        <v>177.43</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>667491</v>
+        <v>532290</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4463</v>
+        <v>4340</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4463</v>
+        <v>4340</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="J9" t="n">
         <v>2028</v>
@@ -891,32 +891,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
+          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>7340</v>
+        <v>2435</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>177.43</v>
+        <v>440.836</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>532290</v>
+        <v>440836</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4340</v>
+        <v>1435</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4340</v>
+        <v>1435</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
         <v>2028</v>
@@ -925,32 +925,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
+          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2435</v>
+        <v>3493</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>440.836</v>
+        <v>436.392</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>440836</v>
+        <v>436392</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1435</v>
+        <v>2493</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1435</v>
+        <v>2493</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="J11" t="n">
         <v>2028</v>
@@ -991,34 +991,136 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [1000ml]/ Шампунь с черным чесноком против выпадения волос</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>404.712</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>161885</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DEOPROCE RINSE - BLACK GARLIC INTENSME ENERGY [1000ml] / Бальзам от выпадения волос Чёрный чеснок</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>394.823</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>157929</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]/ Шампунь с черным чесноком против выпадения волос</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>166.243</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>39898</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
-        <v>61679</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>29000</v>
-      </c>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="n">
-        <v>12890581</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>32679</v>
-      </c>
-      <c r="G13" s="6" t="n">
+      <c r="B16" s="6" t="n">
+        <v>62719</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>28040</v>
+      </c>
+      <c r="D16" s="6" t="inlineStr"/>
+      <c r="E16" s="6" t="n">
+        <v>12377509</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>34679</v>
+      </c>
+      <c r="G16" s="6" t="n">
         <v>65028</v>
       </c>
-      <c r="H13" s="6" t="n">
-        <v>97707</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>13200</v>
-      </c>
-      <c r="J13" s="5" t="inlineStr"/>
+      <c r="H16" s="6" t="n">
+        <v>99707</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>14240</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/Заказ покупателю.xlsx
+++ b/outputs/Заказ покупателю.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12377509</v>
+        <v>12457445</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28040</v>
+        <v>28340</v>
       </c>
     </row>
     <row r="5">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-978762</v>
+        <v>-898826</v>
       </c>
     </row>
   </sheetData>
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -1061,20 +1061,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]/ Шампунь с черным чесноком против выпадения волос</t>
+          <t>ELIZAVECCA - CER-100 Collagen Ceramide Coating Protein Treatment [100ml] / Коллагеновая маска для волос</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>166.243</v>
+        <v>266.453</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>39898</v>
+        <v>79936</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>0</v>
@@ -1086,41 +1086,75 @@
         <v>0</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="J15" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]/ Шампунь с черным чесноком против выпадения волос</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>166.243</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>39898</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
-        <v>62719</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>28040</v>
-      </c>
-      <c r="D16" s="6" t="inlineStr"/>
-      <c r="E16" s="6" t="n">
-        <v>12377509</v>
-      </c>
-      <c r="F16" s="6" t="n">
+      <c r="B17" s="6" t="n">
+        <v>63019</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>28340</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr"/>
+      <c r="E17" s="6" t="n">
+        <v>12457445</v>
+      </c>
+      <c r="F17" s="6" t="n">
         <v>34679</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G17" s="6" t="n">
         <v>65028</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H17" s="6" t="n">
         <v>99707</v>
       </c>
-      <c r="I16" s="6" t="n">
-        <v>14240</v>
-      </c>
-      <c r="J16" s="5" t="inlineStr"/>
+      <c r="I17" s="6" t="n">
+        <v>14540</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/Заказ покупателю.xlsx
+++ b/outputs/Заказ покупателю.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12457445</v>
+        <v>11286825</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28340</v>
+        <v>26340</v>
       </c>
     </row>
     <row r="5">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-898826</v>
+        <v>-2069446</v>
       </c>
     </row>
   </sheetData>
@@ -653,29 +653,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
+          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/Подтягивающий бустер-крем с ретинолом для лица</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>3112</v>
+        <v>9493</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>3000</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>585.3100000000001</v>
+        <v>563.3979999999999</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>1755930</v>
+        <v>1690194</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>112</v>
+        <v>6493</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>112</v>
+        <v>6493</v>
       </c>
       <c r="I3" s="4" t="n">
         <v>600</v>
@@ -687,32 +687,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/Подтягивающий бустер-крем с ретинолом для лица</t>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9493</v>
+        <v>7126</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>3000</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>563.3979999999999</v>
+        <v>509.509</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1690194</v>
+        <v>1528527</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>6493</v>
+        <v>4126</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0</v>
+        <v>25020</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>6493</v>
+        <v>29146</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
         <v>2028</v>
@@ -721,32 +721,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>7126</v>
+        <v>7279</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>3000</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>509.509</v>
+        <v>397.133</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1528527</v>
+        <v>1191399</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>4126</v>
+        <v>4279</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>25020</v>
+        <v>0</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>29146</v>
+        <v>4279</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="J5" t="n">
         <v>2028</v>
@@ -755,32 +755,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
+          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>7279</v>
+        <v>6179</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>3000</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>397.133</v>
+        <v>382.536</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1191399</v>
+        <v>1147608</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>4279</v>
+        <v>3179</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4279</v>
+        <v>3179</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1800</v>
+        <v>4000</v>
       </c>
       <c r="J6" t="n">
         <v>2028</v>
@@ -789,32 +789,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
+          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>6179</v>
+        <v>7463</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>3000</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>382.536</v>
+        <v>222.497</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1147608</v>
+        <v>667491</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3179</v>
+        <v>4463</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3179</v>
+        <v>4463</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4000</v>
+        <v>600</v>
       </c>
       <c r="J7" t="n">
         <v>2028</v>
@@ -823,29 +823,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
+          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>7463</v>
+        <v>3112</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>222.497</v>
+        <v>585.3100000000001</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>667491</v>
+        <v>585310</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4463</v>
+        <v>2112</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4463</v>
+        <v>2112</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>600</v>
@@ -1136,20 +1136,20 @@
         <v>63019</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>28340</v>
+        <v>26340</v>
       </c>
       <c r="D17" s="6" t="inlineStr"/>
       <c r="E17" s="6" t="n">
-        <v>12457445</v>
+        <v>11286825</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>34679</v>
+        <v>36679</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>65028</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>99707</v>
+        <v>101707</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>14540</v>

--- a/outputs/Заказ покупателю.xlsx
+++ b/outputs/Заказ покупателю.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ИТОГО" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЗАКАЗ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="НЕ ВОШЛО" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ДЕРЖИМ СЕБЕ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11286825</v>
+        <v>13292815</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -495,27 +495,27 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26340</v>
+        <v>31240</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Отбор: остаток на складе не меньше, шт</t>
+          <t>Запас себе, месяцев продаж</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3000</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>По каждой позиции даем, шт</t>
+          <t>Минимальная партия в опт, шт</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2069446</v>
+        <v>-63456</v>
       </c>
     </row>
   </sheetData>
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -562,6 +562,9 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -577,40 +580,55 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Спрос, шт/мес</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Приход, шт</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Отгружаем, шт</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Себестоимость, руб</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Сумма, руб</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Останется на складе, шт</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Приход, шт</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>С учетом прихода, шт</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Хватит себе на, мес</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Просил покупатель, шт</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Вердикт</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Срок годности</t>
         </is>
@@ -619,542 +637,1609 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
+          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/Подтягивающий бустер-крем с ретинолом для лица</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>4520</v>
+        <v>9493</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>3000</v>
+        <v>321.7</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>730.246</v>
+        <v>0</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>2190738</v>
+        <v>8200</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1520</v>
+        <v>563.3979999999999</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>40008</v>
+        <v>4619864</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>41528</v>
+        <v>1293</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>1000</v>
+        <v>1293</v>
       </c>
       <c r="J2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>600</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>сбой: карточка потеряла трафик</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/Подтягивающий бустер-крем с ретинолом для лица</t>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>9493</v>
+        <v>7126</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>3000</v>
+        <v>2073.9</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>563.3979999999999</v>
+        <v>25020</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>1690194</v>
+        <v>2800</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>6493</v>
+        <v>509.509</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0</v>
+        <v>1426625</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>6493</v>
+        <v>4326</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>600</v>
+        <v>29346</v>
       </c>
       <c r="J3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
+          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>7126</v>
+        <v>1009</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>509.509</v>
+        <v>0</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1528527</v>
+        <v>500</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>4126</v>
+        <v>1469.545</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>25020</v>
+        <v>734772</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>29146</v>
+        <v>509</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J4" t="n">
+        <v>509</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>мало трафика, судить рано</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>7279</v>
+        <v>1500</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>3000</v>
+        <v>167.8</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>397.133</v>
+        <v>0</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1191399</v>
+        <v>800</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>4279</v>
+        <v>778.668</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0</v>
+        <v>622934</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>4279</v>
+        <v>700</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>1800</v>
+        <v>700</v>
       </c>
       <c r="J5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>избыток запаса</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
+          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>6179</v>
+        <v>1355</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3000</v>
+        <v>182.7</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>382.536</v>
+        <v>0</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1147608</v>
+        <v>600</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3179</v>
+        <v>989.7579999999999</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0</v>
+        <v>593855</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3179</v>
+        <v>755</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4000</v>
+        <v>755</v>
       </c>
       <c r="J6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>избыток запаса</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
+          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>7463</v>
+        <v>3112</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3000</v>
+        <v>605.6</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>222.497</v>
+        <v>0</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>667491</v>
+        <v>1000</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4463</v>
+        <v>585.3100000000001</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0</v>
+        <v>585310</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4463</v>
+        <v>2112</v>
       </c>
       <c r="I7" s="4" t="n">
+        <v>2112</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K7" s="4" t="n">
         <v>600</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3112</v>
+        <v>1375</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1000</v>
+        <v>103.4</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>585.3100000000001</v>
+        <v>0</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>585310</v>
+        <v>900</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2112</v>
+        <v>611.798</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0</v>
+        <v>550618</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2112</v>
+        <v>475</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>600</v>
+        <v>475</v>
       </c>
       <c r="J8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>затоварен: спрос есть, запаса на годы</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>7340</v>
+        <v>7279</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3000</v>
+        <v>1491.1</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>177.43</v>
+        <v>0</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>532290</v>
+        <v>1300</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4340</v>
+        <v>397.133</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0</v>
+        <v>516273</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4340</v>
+        <v>5979</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2000</v>
+        <v>5979</v>
       </c>
       <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2435</v>
+        <v>1422</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1000</v>
+        <v>136.3</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>440.836</v>
+        <v>0</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>440836</v>
+        <v>800</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1435</v>
+        <v>563.552</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0</v>
+        <v>450842</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1435</v>
+        <v>622</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>400</v>
+        <v>622</v>
       </c>
       <c r="J10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>избыток запаса</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
+          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>3493</v>
+        <v>2435</v>
       </c>
       <c r="C11" s="4" t="n">
+        <v>461</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>1000</v>
       </c>
-      <c r="D11" s="4" t="n">
-        <v>436.392</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>436392</v>
-      </c>
       <c r="F11" s="4" t="n">
-        <v>2493</v>
+        <v>440.836</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0</v>
+        <v>440836</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2493</v>
+        <v>1435</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>800</v>
+        <v>1435</v>
       </c>
       <c r="J11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
+          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и пробиотиками</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>3239</v>
+        <v>614</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1000</v>
+        <v>36.5</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>436.392</v>
+        <v>0</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>436392</v>
+        <v>400</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2239</v>
+        <v>1096.425</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0</v>
+        <v>438570</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2239</v>
+        <v>214</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>400</v>
+        <v>214</v>
       </c>
       <c r="J12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>затоварен: спрос есть, запаса на годы</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [1000ml]/ Шампунь с черным чесноком против выпадения волос</t>
+          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>400</v>
+        <v>3493</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>400</v>
+        <v>316.6</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>404.712</v>
+        <v>0</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>161885</v>
+        <v>1000</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0</v>
+        <v>436.392</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0</v>
+        <v>436392</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0</v>
+        <v>2493</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>400</v>
+        <v>2493</v>
       </c>
       <c r="J13" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>800</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>избыток запаса</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DEOPROCE RINSE - BLACK GARLIC INTENSME ENERGY [1000ml] / Бальзам от выпадения волос Чёрный чеснок</t>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>3239</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>1514</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>436.392</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>436392</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>2239</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>2239</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K14" s="4" t="n">
         <v>400</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>394.823</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>157929</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ELIZAVECCA - CER-100 Collagen Ceramide Coating Protein Treatment [100ml] / Коллагеновая маска для волос</t>
+          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>300</v>
+        <v>966</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>266.453</v>
+        <v>360</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>79936</v>
+        <v>800</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0</v>
+        <v>533.423</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0</v>
+        <v>426738</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="J15" t="n">
+        <v>526</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>мало трафика, судить рано</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>650</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>813.901</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>325560</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>затоварен: спрос есть, запаса на годы</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [1000ml]/ Шампунь с черным чесноком против выпадения волос</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>404.712</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>161885</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DEOPROCE RINSE - BLACK GARLIC INTENSME ENERGY [1000ml] / Бальзам от выпадения волос Чёрный чеснок</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>394.823</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>157929</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ELIZAVECCA - CER-100 Collagen Ceramide Coating Protein Treatment [100ml] / Коллагеновая маска для волос</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>266.453</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>79936</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>избыток запаса</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>118.965</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>47586</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>неликвид: смотрят и не берут</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>02,2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]/ Шампунь с черным чесноком против выпадения волос</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B21" s="4" t="n">
         <v>240</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C21" s="4" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>240</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="F21" s="4" t="n">
         <v>166.243</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>39898</v>
       </c>
-      <c r="F16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="4" t="n">
+      <c r="H21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4" t="n">
         <v>240</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
         <v>2028</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>JIGOTT - Placenta Real Ampoule Mask [27ml] / Ампульная маска с плацентой</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>12500</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>JIGOTT - Pearl Real Ampoule Mask [27ml] / ампульная маска для лица с жемчугом</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>12500</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>JIGOTT - Lotus Real Ampoule Mask [27ml] / Ампульная маска с экстрактом лотоса</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>12500</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>JIGOTT - Hyaluronic Acid Real Ampoule Mask [27ml] / Ампульная маска с гиалуроновой кислотой</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>12500</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>JIGOTT - Honey Real Ampoule Mask [27ml] / Ампульная маска с экстрактом меда</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>12500</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>JIGOTT - Green Tea Real Ampoule Mask [27ml] / Ампульная маска с экстрактом зеленого чая</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>12500</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>JIGOTT - Cucumber Real Ampoule Mask [27ml] / Тканевая маска с экстрактом огурца</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>12500</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>JIGOTT - Collagen Real Ampoule Mask [27ml] / Ампульная маска с коллагеном</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>12500</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>JIGOTT - Caviar Real Ampoule Mask [27ml] / Ампульная маска с экстрактом икры</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>12500</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>JIGOTT - Camellia Real Ampoule Mask [27ml] / Ампульная маска с экстрактом камелии</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>12500</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>JIGOTT - Black Snail Real Ampoule Mask [27ml] / Ампульная маска с экстрактом слизи черной улитки</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>12500</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>JIGOTT - Aloe Real Ampoule Mask [27ml] / Ампульная маска с экстрактом алое</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>12500</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>JIGOTT - Pomegranate Real Ampoule Mask [27ml] / Ампульная маска с экстрактом граната</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>12500</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>JIGOTT - Potato Real Ampoule Mask [27ml] / Ампульная маска с экстрактом картофеля</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>12500</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>JIGOTT - Red Ginseng Real Ampoule Mask [27ml] / Ампульная маска с красным женьшенем</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>12500</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>JIGOTT - Vitamin Real Ampoule Mask [27ml] / Ампульная маска с витаминами</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>12500</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>690</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n">
-        <v>63019</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>26340</v>
-      </c>
-      <c r="D17" s="6" t="inlineStr"/>
-      <c r="E17" s="6" t="n">
-        <v>11286825</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>36679</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>65028</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>101707</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>14540</v>
-      </c>
-      <c r="J17" s="5" t="inlineStr"/>
+      <c r="B38" s="6" t="n">
+        <v>65848</v>
+      </c>
+      <c r="C38" s="6" t="inlineStr"/>
+      <c r="D38" s="6" t="n">
+        <v>25380</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>31240</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr"/>
+      <c r="G38" s="6" t="n">
+        <v>13292815</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>34608</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>59988</v>
+      </c>
+      <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="6" t="n">
+        <v>28260</v>
+      </c>
+      <c r="L38" s="5" t="inlineStr"/>
+      <c r="M38" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1167,7 +2252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -1175,6 +2260,8 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1190,740 +2277,1050 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Спрос, шт/мес</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Нужно себе, шт</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Просил покупатель, шт</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Себестоимость, руб</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Сумма по его заявке, руб</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Вердикт</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>1355</v>
+        <v>7340</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>450</v>
+        <v>2215.2</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>989.7579999999999</v>
+        <v>8861</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>445391</v>
+        <v>2000</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>354860</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JMSOLUTION - MASK PACK DISNEY [30ml*10ea] - ассорти набор из 10шт</t>
+          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>832</v>
+        <v>344</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>832</v>
+        <v>265.8</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>509.52</v>
+        <v>1063</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>423921</v>
+        <v>344</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>69580</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ходовой, запас кончается</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>941</v>
+        <v>200</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>400</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>847.528</v>
+        <v>324</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>339011</v>
+        <v>200</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>40313</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>259</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1202.256</v>
+        <v>320</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>311384</v>
+        <v>300</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>60469</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>избыток запаса</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1009</v>
+        <v>260</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>200</v>
+        <v>54.4</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1469.545</v>
+        <v>218</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>293909</v>
+        <v>260</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>52407</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>затоварен: спрос есть, запаса на годы</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
+          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>650</v>
+        <v>6179</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>350</v>
+        <v>1989.2</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>813.901</v>
+        <v>7957</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>284865</v>
+        <v>4000</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>1530144</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>624</v>
+        <v>900</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>300</v>
+        <v>555.1</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>808.874</v>
+        <v>2220</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>242662</v>
+        <v>500</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>237078</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ходовой, запас кончается</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
+          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>900</v>
+        <v>860</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>500</v>
+        <v>613.4</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>474.155</v>
+        <v>2454</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>237078</v>
+        <v>400</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>138090</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ходовой, запас кончается</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>759</v>
+        <v>901</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>300</v>
+        <v>226</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>711.513</v>
+        <v>904</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>213454</v>
+        <v>400</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>171802</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea] / гидрогелевые патчи для глаз с золотом</t>
+          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка роллер для глаз</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>405</v>
+        <v>156</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>405</v>
+        <v>213.9</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>457.0059999999999</v>
+        <v>856</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>185087</v>
+        <v>156</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>39765</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>сбой: карточка потеряла трафик</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
+          <t>FARMSTAY - Collagen Water Full Moist Cream [100g] / Увлажняющий крем с коллагеном</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2435</v>
+        <v>200</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>400</v>
+        <v>170.5</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>440.836</v>
+        <v>682</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>176334</v>
+        <v>200</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>106572</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ходовой, запас кончается</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>901</v>
+        <v>300</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>400</v>
+        <v>85.2</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>429.506</v>
+        <v>341</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>171802</v>
+        <v>300</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>53285</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>сбой: карточка потеряла трафик</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
+          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>1422</v>
+        <v>941</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>300</v>
+        <v>368.3</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>563.552</v>
+        <v>1473</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>169066</v>
+        <v>400</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>339011</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea] / Охлаждающие гидрогелевые патчи для глаз с экстрактом агавы</t>
+          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>360</v>
+        <v>7463</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>360</v>
+        <v>1908.1</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>457.0059999999999</v>
+        <v>7632</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>164522</v>
+        <v>600</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>133498</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [1000ml]/ Шампунь с черным чесноком против выпадения волос</t>
+          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозрастной с муцином улитки</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>400</v>
+        <v>499.9</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>404.712</v>
+        <v>2000</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>161885</v>
+        <v>300</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>61334</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>сбой: карточка потеряла трафик</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DEOPROCE RINSE - BLACK GARLIC INTENSME ENERGY [1000ml] / Бальзам от выпадения волос Чёрный чеснок</t>
+          <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной крем с экстрактом ласточкиного гнезда</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>400</v>
+        <v>1614</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>400</v>
+        <v>467.2</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>394.823</v>
+        <v>1869</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>157929</v>
+        <v>600</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>133498</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>сбой: карточка потеряла трафик</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>200</v>
+        <v>273.6</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>778.668</v>
+        <v>1094</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>155734</v>
+        <v>300</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>87569</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>сбой: карточка потеряла трафик</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с коллагеном и коэнзимом Q10</t>
+          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>360</v>
+        <v>800</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>360</v>
+        <v>292.6</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>423.555</v>
+        <v>1170</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>152480</v>
+        <v>300</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>87569</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
+          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml] / Тонер для лица увлажняющий с экстрактом алоэ</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>966</v>
+        <v>100</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>280</v>
+        <v>224.3</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>533.423</v>
+        <v>897</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>149358</v>
+        <v>100</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>29190</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>сбой: карточка потеряла трафик</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
+          <t>JMSOLUTION ACTIVE BLACK CAVIAR MASK [30ml*10ea] / Ультратонкая тканевая маска с черной икрой</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>860</v>
+        <v>110</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>345.224</v>
+        <v>55</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>138090</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>41415</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной крем с экстрактом ласточкиного гнезда</t>
+          <t>JMSOLUTION - Active Golden Caviar Nourishing Mask [30ml*10ea] / Ультратонкая тканевая маска с золотом и икрой</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>1614</v>
+        <v>110</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>222.497</v>
+        <v>55</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>133498</v>
+        <v>110</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>41415</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
+          <t>JMSOLUTION - Active Jellyfish Vital Mask [30ml*10ea] / Ультратонкая тканевая маска с экстрактом медузы</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>1375</v>
+        <v>110</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>611.798</v>
+        <v>55</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>122360</v>
+        <v>110</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>41415</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и пробиотиками</t>
+          <t>JMSOLUTION - Active Birds Nest Moisture Mask [30ml*10ea] / Ультратонкая тканевая маска с ласточкиным гнездом</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>614</v>
+        <v>110</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1096.425</v>
+        <v>55</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>109642</v>
+        <v>110</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>41415</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
+          <t>JMSOLUTION GLORY AQUA FULLERENE MASK DELUXE</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>397</v>
+        <v>110</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1071.444</v>
+        <v>55</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>107144</v>
+        <v>110</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>54492</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs] / Охлаждающая гидрогелевая маска для лица с экстрактом агавы</t>
+          <t>JMSOLUTION  JMSOLUTION - Glory Aqua TOCOPHEROL VITAMIN C MASK PLUS [30ml*10ea] / Тканевая маска</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>600</v>
+        <v>110</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>535.051</v>
+        <v>55</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>107010</v>
+        <v>110</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>54492</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Cream [100g] / Увлажняющий крем с коллагеном</t>
+          <t>JMSOLUTION PANTHELENE INTENSIVE BARRIER MASK</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>532.862</v>
+        <v>55</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>106572</v>
+        <v>110</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>54492</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
+          <t>JMSOLUTION - The Natural Cordyceps Melitaris Mask Moisture [30ml*10ea] / Тканевая маска для лица с экстрактом кордицепса и комплексом аминокислот</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>535.359</v>
+        <v>55</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>96365</v>
+        <v>110</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>38532</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с черным жемчугом и золотом</t>
+          <t>JMSOLUTION - Water Luminous S.O.S. Ringer Mask Black [35ml*10ea] / Ультраувлажняющая тканевая маска</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>216</v>
+        <v>110</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>426.437</v>
+        <v>55</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>92110</v>
+        <v>110</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>54492</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
+          <t>JMSOLUTION GREEN DEAR TIGER CICA MASK PURE 30ml*10ea / Регенерирующая маска для лица с центеллой</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>800</v>
+        <v>110</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>291.896</v>
+        <v>55</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>87569</v>
+        <v>110</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>41415</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
+          <t>JMSOLUTION - MASK PACK DISNEY [30ml*10ea] - ассорти набор из 10шт</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>800</v>
+        <v>832</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>300</v>
+        <v>206.1</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>291.896</v>
+        <v>824</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>87569</v>
+        <v>832</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>423921</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
+          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>90</v>
+        <v>759</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>90</v>
+        <v>261.1</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>950.521</v>
+        <v>1044</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>85547</v>
+        <v>300</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>213454</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ELIZAVECCA - CER-100 Collagen Ceramide Coating Protein Treatment [100ml] / Коллагеновая маска для волос</t>
+          <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
+        <v>624</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>198.4</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>794</v>
+      </c>
+      <c r="E33" s="4" t="n">
         <v>300</v>
       </c>
-      <c r="C33" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>266.453</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>79936</v>
+      <c r="F33" s="4" t="n">
+        <v>242662</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>сбой: карточка потеряла трафик</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом и экстрактом улитки</t>
+          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>150</v>
+        <v>179.4</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>525.987</v>
+        <v>718</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>78898</v>
+        <v>80</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>75064</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ходовой, запас кончается</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
+          <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с коллагеном и коэнзимом Q10</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>80</v>
+        <v>360</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>80</v>
+        <v>174.4</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>938.3</v>
+        <v>698</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>75064</v>
+        <v>360</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>152480</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>сбой: карточка потеряла трафик</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea] / Смягчающие гидрогелевые патчи для глаз с экстрактом артишока</t>
+          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>156</v>
+        <v>85.8</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>457.0059999999999</v>
+        <v>343</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>71293</v>
+        <v>180</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>96365</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea] / Смягчающие гидрогелевые патчи для глаз с экстрактом артишока</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>344</v>
+        <v>156</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>344</v>
+        <v>142.6</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>202.268</v>
+        <v>570</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>69580</v>
+        <v>156</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>71293</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ходовой, запас кончается</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с золотом и улиткой</t>
+          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>144</v>
+        <v>89</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>144</v>
+        <v>24.7</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>457.0059999999999</v>
+        <v>99</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>65809</v>
+        <v>89</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>57887</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
+          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea] / Тонизирующие гидрогелевые патчи для глаз с экстрактом какао</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>55</v>
+        <v>31.8</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>1162.92</v>
+        <v>127</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>63961</v>
+        <v>72</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>32904</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -1936,998 +3333,687 @@
         <v>117</v>
       </c>
       <c r="C40" s="4" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="E40" s="4" t="n">
         <v>117</v>
       </c>
-      <c r="D40" s="4" t="n">
-        <v>535.359</v>
-      </c>
-      <c r="E40" s="4" t="n">
+      <c r="F40" s="4" t="n">
         <v>62637</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>избыток запаса</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозрастной с муцином улитки</t>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с черным жемчугом и золотом</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>500</v>
+        <v>216</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>300</v>
+        <v>322.9</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>204.446</v>
+        <v>1292</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>61334</v>
+        <v>216</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>92110</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ходовой, запас кончается</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
+          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea] / Охлаждающие гидрогелевые патчи для глаз с экстрактом агавы</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>300</v>
+        <v>264.7</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>201.564</v>
+        <v>1059</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>60469</v>
+        <v>360</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>164522</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ходовой, запас кончается</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с золотом и улиткой</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>89</v>
+        <v>144</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>89</v>
+        <v>213.9</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>650.419</v>
+        <v>856</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>57887</v>
+        <v>144</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>65809</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>сбой: карточка потеряла трафик</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом</t>
+          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea] / гидрогелевые патчи для глаз с золотом</t>
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>100</v>
+        <v>123.9</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>557.876</v>
+        <v>496</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>55788</v>
+        <v>405</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>185087</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>сбой: карточка потеряла трафик</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Water Luminous S.O.S. Ringer Mask Black [35ml*10ea] / Ультраувлажняющая тканевая маска</t>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]/ Гидрогелевые патчи для глаз с черным жемчугом и золотом 1 пара</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>495.385</v>
+        <v>160</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>54492</v>
+        <v>320</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>25076</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>JMSOLUTION  JMSOLUTION - Glory Aqua TOCOPHEROL VITAMIN C MASK PLUS [30ml*10ea] / Тканевая маска</t>
+          <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs] / гидрогелевые патчи для глаз с золотом 1 пара</t>
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>110</v>
+        <v>428</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>495.385</v>
+        <v>214</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>54492</v>
+        <v>428</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>33540</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>JMSOLUTION PANTHELENE INTENSIVE BARRIER MASK</t>
+          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs] / Охлаждающая гидрогелевая маска для лица с экстрактом агавы</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>110</v>
+        <v>167.5</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>495.385</v>
+        <v>670</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>54492</v>
+        <v>200</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>107010</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>JMSOLUTION GLORY AQUA FULLERENE MASK DELUXE</t>
+          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом</t>
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>110</v>
+        <v>390</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>110</v>
+        <v>205</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>495.385</v>
+        <v>820</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>54492</v>
+        <v>100</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>55788</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>сбой: карточка потеряла трафик</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
+          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs] / Тонизирующая гидрогелевая маска для лица с экстрактом какао</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>300</v>
+        <v>90</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>300</v>
+        <v>194.6</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>177.617</v>
+        <v>778</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>53285</v>
+        <v>90</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>49189</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>сбой: карточка потеряла трафик</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]/Сыворотка для выравнивания тона и рельефа кожи лица</t>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs] / Смягчающая гидрогелевая маска для лица с экстрактом артишока</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>70</v>
+        <v>198.7</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>756.3380000000001</v>
+        <v>795</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>52944</v>
+        <v>60</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>32904</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>сбой: спрос был, конверсия упала</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом и экстрактом улитки</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>260</v>
+        <v>150</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>260</v>
+        <v>104.9</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>201.564</v>
+        <v>420</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>52407</v>
+        <v>150</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>78898</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs] / Тонизирующая гидрогелевая маска для лица с экстрактом какао</t>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с черным жемчугом и золотом</t>
         </is>
       </c>
       <c r="B52" s="4" t="n">
         <v>90</v>
       </c>
       <c r="C52" s="4" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>507</v>
+      </c>
+      <c r="E52" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="D52" s="4" t="n">
-        <v>546.546</v>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>49189</v>
+      <c r="F52" s="4" t="n">
+        <v>47327</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>сбой: карточка потеряла трафик</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сыворотка с экстрактом нони для лица</t>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>57</v>
+        <v>259</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>57</v>
+        <v>158</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>840.213</v>
+        <v>632</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>47892</v>
+        <v>259</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>311384</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>сбой: карточка потеряла трафик</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с черным жемчугом и золотом</t>
+          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица увлажняющая с центеллой</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>90</v>
+        <v>83.5</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>525.855</v>
+        <v>0</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>47327</v>
+        <v>32</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>28854</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>неликвид: смотрят и не берут</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>JMSOLUTION GREEN DEAR TIGER CICA MASK PURE 30ml*10ea / Регенерирующая маска для лица с центеллой</t>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>110</v>
+        <v>18.4</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>376.497</v>
+        <v>0</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>41415</v>
+        <v>30</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>12140</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>неликвид: смотрят и не берут</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Active Golden Caviar Nourishing Mask [30ml*10ea] / Ультратонкая тканевая маска с золотом и икрой</t>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>110</v>
+        <v>9.5</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>376.497</v>
+        <v>38</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>41415</v>
+        <v>55</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>63961</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>сбой: карточка потеряла трафик</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Active Birds Nest Moisture Mask [30ml*10ea] / Ультратонкая тканевая маска с ласточкиным гнездом</t>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>110</v>
+        <v>7.7</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>376.497</v>
+        <v>31</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>41415</v>
+        <v>31</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>28831</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Active Jellyfish Vital Mask [30ml*10ea] / Ультратонкая тканевая маска с экстрактом медузы</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>110</v>
+        <v>204.7</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>376.497</v>
+        <v>819</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>41415</v>
+        <v>200</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>21327</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>сбой: спрос был, конверсия упала</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>JMSOLUTION ACTIVE BLACK CAVIAR MASK [30ml*10ea] / Ультратонкая тканевая маска с черной икрой</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]/Крем для выравнивания тона и рельефа кожи лица</t>
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>110</v>
+        <v>15.4</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>376.497</v>
+        <v>62</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>41415</v>
+        <v>13</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>8915</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>сбой: карточка потеряла трафик</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка)</t>
+          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
         </is>
       </c>
       <c r="B60" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>200</v>
+        <v>10.7</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>201.564</v>
+        <v>43</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>40313</v>
+        <v>90</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>85547</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>затоварен: спрос есть, запаса на годы</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]/ Шампунь с черным чесноком против выпадения волос</t>
+          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сыворотка с экстрактом нони для лица</t>
         </is>
       </c>
       <c r="B61" s="4" t="n">
-        <v>240</v>
+        <v>57</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>240</v>
+        <v>13.7</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>166.243</v>
+        <v>55</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>39898</v>
+        <v>57</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>47892</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка роллер для глаз</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]/Сыворотка для выравнивания тона и рельефа кожи лица</t>
         </is>
       </c>
       <c r="B62" s="4" t="n">
-        <v>156</v>
+        <v>70</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>156</v>
+        <v>8.6</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>254.903</v>
+        <v>34</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>39765</v>
+        <v>70</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>52944</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>избыток запаса</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>JMSOLUTION - The Natural Cordyceps Melitaris Mask Moisture [30ml*10ea] / Тканевая маска для лица с экстрактом кордицепса и комплексом аминокислот</t>
+          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
         </is>
       </c>
       <c r="B63" s="4" t="n">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="C63" s="4" t="n">
-        <v>110</v>
+        <v>6.8</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>350.295</v>
+        <v>27</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>38532</v>
+        <v>23</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>18205</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs] / гидрогелевые патчи для глаз с золотом 1 пара</t>
+          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
         </is>
       </c>
       <c r="B64" s="4" t="n">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>428</v>
+        <v>0</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>78.36399999999999</v>
+        <v>198</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>33540</v>
+        <v>100</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>107144</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>мало трафика, судить рано</t>
+        </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea] / Тонизирующие гидрогелевые патчи для глаз с экстрактом какао</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>457.0059999999999</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>32904</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs] / Смягчающая гидрогелевая маска для лица с экстрактом артишока</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="C66" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>548.394</v>
-      </c>
-      <c r="E66" s="4" t="n">
-        <v>32904</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>JIGOTT - Aloe Real Ampoule Mask [27ml] / Ампульная маска с экстрактом алое</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="C67" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>29750</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>JIGOTT - Honey Real Ampoule Mask [27ml] / Ампульная маска с экстрактом меда</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="C68" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E68" s="4" t="n">
-        <v>29750</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>JIGOTT - Green Tea Real Ampoule Mask [27ml] / Ампульная маска с экстрактом зеленого чая</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="C69" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="D69" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E69" s="4" t="n">
-        <v>29750</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>JIGOTT - Cucumber Real Ampoule Mask [27ml] / Тканевая маска с экстрактом огурца</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="C70" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="D70" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E70" s="4" t="n">
-        <v>29750</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>JIGOTT - Collagen Real Ampoule Mask [27ml] / Ампульная маска с коллагеном</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="C71" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E71" s="4" t="n">
-        <v>29750</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>JIGOTT - Caviar Real Ampoule Mask [27ml] / Ампульная маска с экстрактом икры</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="C72" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="D72" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E72" s="4" t="n">
-        <v>29750</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>JIGOTT - Camellia Real Ampoule Mask [27ml] / Ампульная маска с экстрактом камелии</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="C73" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="D73" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E73" s="4" t="n">
-        <v>29750</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>JIGOTT - Black Snail Real Ampoule Mask [27ml] / Ампульная маска с экстрактом слизи черной улитки</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="C74" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="D74" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E74" s="4" t="n">
-        <v>29750</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>JIGOTT - Hyaluronic Acid Real Ampoule Mask [27ml] / Ампульная маска с гиалуроновой кислотой</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="C75" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="D75" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E75" s="4" t="n">
-        <v>29750</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>JIGOTT - Vitamin Real Ampoule Mask [27ml] / Ампульная маска с витаминами</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="C76" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="D76" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E76" s="4" t="n">
-        <v>29750</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>JIGOTT - Pearl Real Ampoule Mask [27ml] / ампульная маска для лица с жемчугом</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="C77" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E77" s="4" t="n">
-        <v>29750</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>JIGOTT - Potato Real Ampoule Mask [27ml] / Ампульная маска с экстрактом картофеля</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="C78" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E78" s="4" t="n">
-        <v>29750</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>JIGOTT - Red Ginseng Real Ampoule Mask [27ml] / Ампульная маска с красным женьшенем</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="C79" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E79" s="4" t="n">
-        <v>29750</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>JIGOTT - Placenta Real Ampoule Mask [27ml] / Ампульная маска с плацентой</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="C80" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E80" s="4" t="n">
-        <v>29750</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>JIGOTT - Pomegranate Real Ampoule Mask [27ml] / Ампульная маска с экстрактом граната</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E81" s="4" t="n">
-        <v>29750</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>JIGOTT - Lotus Real Ampoule Mask [27ml] / Ампульная маска с экстрактом лотоса</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="C82" s="4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="D82" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E82" s="4" t="n">
-        <v>29750</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml] / Тонер для лица увлажняющий с экстрактом алоэ</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="C83" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D83" s="4" t="n">
-        <v>291.896</v>
-      </c>
-      <c r="E83" s="4" t="n">
-        <v>29190</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица увлажняющая с центеллой</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="C84" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="D84" s="4" t="n">
-        <v>901.692</v>
-      </c>
-      <c r="E84" s="4" t="n">
-        <v>28854</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="C85" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="D85" s="4" t="n">
-        <v>930.039</v>
-      </c>
-      <c r="E85" s="4" t="n">
-        <v>28831</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]/ Гидрогелевые патчи для глаз с черным жемчугом и золотом 1 пара</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="n">
-        <v>320</v>
-      </c>
-      <c r="C86" s="4" t="n">
-        <v>320</v>
-      </c>
-      <c r="D86" s="4" t="n">
-        <v>78.36399999999999</v>
-      </c>
-      <c r="E86" s="4" t="n">
-        <v>25076</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="C87" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="D87" s="4" t="n">
-        <v>118.965</v>
-      </c>
-      <c r="E87" s="4" t="n">
-        <v>23793</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C88" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="D88" s="4" t="n">
-        <v>106.634</v>
-      </c>
-      <c r="E88" s="4" t="n">
-        <v>21327</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="C89" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="D89" s="4" t="n">
-        <v>791.538</v>
-      </c>
-      <c r="E89" s="4" t="n">
-        <v>18205</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="C90" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="D90" s="4" t="n">
-        <v>404.679</v>
-      </c>
-      <c r="E90" s="4" t="n">
-        <v>12140</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]/Крем для выравнивания тона и рельефа кожи лица</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="C91" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="D91" s="4" t="n">
-        <v>685.7729999999999</v>
-      </c>
-      <c r="E91" s="4" t="n">
-        <v>8915</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr"/>
-      <c r="C92" s="6" t="n">
-        <v>35229</v>
-      </c>
-      <c r="D92" s="6" t="inlineStr"/>
-      <c r="E92" s="6" t="n">
-        <v>8170278</v>
-      </c>
+      <c r="B65" s="6" t="inlineStr"/>
+      <c r="C65" s="6" t="inlineStr"/>
+      <c r="D65" s="6" t="inlineStr"/>
+      <c r="E65" s="6" t="n">
+        <v>18769</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>7342680</v>
+      </c>
+      <c r="G65" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
